--- a/output/2026-09-15/enriched_analysis.xlsx
+++ b/output/2026-09-15/enriched_analysis.xlsx
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.66</v>
+        <v>3.653</v>
       </c>
       <c r="Q2" t="n">
-        <v>2894</v>
+        <v>2899</v>
       </c>
       <c r="R2" t="n">
         <v>22.7</v>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="Q3" t="n">
-        <v>2661</v>
+        <v>2691</v>
       </c>
       <c r="R3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="S3" t="n">
         <v>36</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.133</v>
+        <v>0.134</v>
       </c>
       <c r="Q4" t="n">
-        <v>2364</v>
+        <v>2342</v>
       </c>
       <c r="R4" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="S4" t="n">
         <v>-3</v>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.885</v>
+        <v>0.877</v>
       </c>
       <c r="Q6" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="R6" t="n">
-        <v>8.890000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="S6" t="n">
         <v>17</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.814</v>
+        <v>2.803</v>
       </c>
       <c r="Q7" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="R7" t="n">
         <v>11.6</v>
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="Q8" t="n">
-        <v>1418</v>
+        <v>1343</v>
       </c>
       <c r="R8" t="n">
-        <v>19.1</v>
+        <v>18.1</v>
       </c>
       <c r="S8" t="n">
         <v>55</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.638</v>
+        <v>0.645</v>
       </c>
       <c r="Q9" t="n">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.323</v>
+        <v>0.324</v>
       </c>
       <c r="Q10" t="n">
-        <v>2629</v>
+        <v>2617</v>
       </c>
       <c r="R10" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.282</v>
+        <v>2.285</v>
       </c>
       <c r="Q11" t="n">
-        <v>2611</v>
+        <v>2608</v>
       </c>
       <c r="R11" t="n">
         <v>205</v>
@@ -2634,10 +2634,10 @@
         <v>0.046</v>
       </c>
       <c r="Q12" t="n">
-        <v>15522</v>
+        <v>15611</v>
       </c>
       <c r="R12" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="S12" t="n">
         <v>83</v>
@@ -2813,13 +2813,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="R13" t="n">
-        <v>62.1</v>
+        <v>61.8</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -3178,10 +3178,10 @@
         <v>0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="R15" t="n">
-        <v>8.779999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="S15" t="n">
         <v>7</v>
@@ -3360,10 +3360,10 @@
         <v>0.013</v>
       </c>
       <c r="Q16" t="n">
-        <v>16119</v>
+        <v>16130</v>
       </c>
       <c r="R16" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="S16" t="n">
         <v>16</v>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.397</v>
+        <v>0.411</v>
       </c>
       <c r="Q17" t="n">
-        <v>1138</v>
+        <v>1099</v>
       </c>
       <c r="R17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="S17" t="n">
         <v>21</v>
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.537</v>
+        <v>0.532</v>
       </c>
       <c r="Q18" t="n">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="R18" t="n">
-        <v>1261</v>
+        <v>1274</v>
       </c>
       <c r="S18" t="n">
         <v>-61</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.612</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="Q20" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="R20" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="S20" t="n">
         <v>24</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
       <c r="Q22" t="n">
-        <v>1558</v>
+        <v>1574</v>
       </c>
       <c r="R22" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="S22" t="n">
         <v>581</v>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.082</v>
+        <v>1.081</v>
       </c>
       <c r="Q23" t="n">
-        <v>9494</v>
+        <v>9503</v>
       </c>
       <c r="R23" t="n">
         <v>12.5</v>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="Q24" t="n">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="R24" t="n">
-        <v>6.14</v>
+        <v>6.04</v>
       </c>
       <c r="S24" t="n">
         <v>118</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.2</v>
+        <v>0.198</v>
       </c>
       <c r="Q25" t="n">
-        <v>854</v>
+        <v>864</v>
       </c>
       <c r="R25" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="S25" t="n">
         <v>19</v>
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="Q26" t="n">
-        <v>1960</v>
+        <v>1986</v>
       </c>
       <c r="R26" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -5350,10 +5350,10 @@
         <v>0.038</v>
       </c>
       <c r="Q27" t="n">
-        <v>3542</v>
+        <v>3529</v>
       </c>
       <c r="R27" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="S27" t="n">
         <v>-4</v>
@@ -5714,10 +5714,10 @@
         <v>0.007</v>
       </c>
       <c r="Q29" t="n">
-        <v>5632</v>
+        <v>5640</v>
       </c>
       <c r="R29" t="n">
-        <v>9.51</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>43</v>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.199</v>
+        <v>0.201</v>
       </c>
       <c r="Q30" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="R30" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="S30" t="n">
         <v>21</v>
@@ -6075,13 +6075,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.502</v>
+        <v>0.507</v>
       </c>
       <c r="Q31" t="n">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="R31" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="S31" t="n">
         <v>-1</v>
@@ -6257,13 +6257,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.594</v>
+        <v>0.598</v>
       </c>
       <c r="Q32" t="n">
-        <v>2298</v>
+        <v>2281</v>
       </c>
       <c r="R32" t="n">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -6439,13 +6439,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.269</v>
+        <v>0.271</v>
       </c>
       <c r="Q33" t="n">
-        <v>1103</v>
+        <v>1095</v>
       </c>
       <c r="R33" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="S33" t="n">
         <v>12</v>
@@ -6621,13 +6621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="Q34" t="n">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="R34" t="n">
-        <v>95.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.391</v>
+        <v>0.396</v>
       </c>
       <c r="Q35" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="R35" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S35" t="n">
         <v>246</v>
@@ -6988,7 +6988,7 @@
         <v>0.097</v>
       </c>
       <c r="Q36" t="n">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="R36" t="n">
         <v>13.8</v>
@@ -7170,7 +7170,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>53164</v>
+        <v>53053</v>
       </c>
       <c r="R37" t="n">
         <v>45</v>
@@ -7297,12 +7297,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7314,87 +7314,85 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>207.79</v>
+        <v>592.2</v>
       </c>
       <c r="J38" t="n">
-        <v>210.84</v>
+        <v>593.62</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.4</v>
+        <v>-0.2</v>
       </c>
       <c r="L38" t="n">
-        <v>67.04000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="M38" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="N38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.21</v>
+        <v>0.027</v>
       </c>
       <c r="Q38" t="n">
-        <v>200</v>
-      </c>
-      <c r="R38" t="n">
-        <v>24.9</v>
-      </c>
+        <v>928</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="T38" t="n">
-        <v>0.03</v>
+        <v>5</v>
       </c>
       <c r="U38" t="n">
-        <v>16</v>
+        <v>-152</v>
       </c>
       <c r="V38" t="n">
-        <v>0.03</v>
+        <v>-6.5</v>
       </c>
       <c r="W38" t="n">
-        <v>7.91</v>
+        <v>9.24</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.16</v>
+        <v>6</v>
       </c>
       <c r="AA38" t="n">
-        <v>208.64</v>
+        <v>590.46</v>
       </c>
       <c r="AB38" t="n">
-        <v>195.46</v>
+        <v>545.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.1</v>
+        <v>17.9</v>
       </c>
       <c r="AD38" t="n">
-        <v>210.8429673885985</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AE38" t="n">
-        <v>-1.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -7403,92 +7401,92 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AL38" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AM38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
         <v>2</v>
       </c>
-      <c r="AO38" t="n">
-        <v>4</v>
-      </c>
       <c r="AP38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AQ38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AR38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AS38" t="n">
-        <v>1087797</v>
+        <v>322003</v>
       </c>
       <c r="AT38" t="n">
-        <v>1371280</v>
+        <v>1288195</v>
       </c>
       <c r="AU38" t="n">
-        <v>4234781</v>
+        <v>2458195</v>
       </c>
       <c r="AV38" t="n">
-        <v>4234781</v>
+        <v>2458195</v>
       </c>
       <c r="AW38" t="n">
-        <v>4234781</v>
+        <v>2458195</v>
       </c>
       <c r="AX38" t="n">
-        <v>1087797</v>
+        <v>322003</v>
       </c>
       <c r="AY38" t="n">
-        <v>4234781</v>
+        <v>2458195</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0.2569</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7496,157 +7494,157 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
+        <v>13</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>207.79</v>
+      </c>
+      <c r="J39" t="n">
+        <v>210.84</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>67.04000000000001</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N39" t="n">
+        <v>9</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>194</v>
+      </c>
+      <c r="R39" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>12</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U39" t="n">
+        <v>16</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W39" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>208.64</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>195.46</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>210.8429673885985</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1206.1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1104.34</v>
-      </c>
-      <c r="K39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L39" t="n">
-        <v>60.82</v>
-      </c>
-      <c r="M39" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>12-06-2026</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>346060</v>
-      </c>
-      <c r="R39" t="n">
-        <v>19</v>
-      </c>
-      <c r="S39" t="n">
-        <v>7</v>
-      </c>
-      <c r="T39" t="n">
-        <v>4158</v>
-      </c>
-      <c r="U39" t="n">
-        <v>44</v>
-      </c>
-      <c r="V39" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="W39" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Y39" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1282.03</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1380.71</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1104.337889591841</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>12-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>12-06-2026</t>
-        </is>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1087797</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1371280</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>4234781</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>4234781</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>4234781</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1087797</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>4234781</v>
       </c>
       <c r="AZ39" t="n">
         <v>1</v>
@@ -7655,18 +7653,18 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>0.2569</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -7678,87 +7676,87 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>126.87</v>
+        <v>1206.1</v>
       </c>
       <c r="J40" t="n">
-        <v>105.19</v>
+        <v>1104.34</v>
       </c>
       <c r="K40" t="n">
-        <v>20.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>67.15000000000001</v>
+        <v>60.82</v>
       </c>
       <c r="M40" t="n">
-        <v>2.63</v>
+        <v>5.22</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.052</v>
+        <v>0.002</v>
       </c>
       <c r="Q40" t="n">
-        <v>5010</v>
+        <v>346752</v>
       </c>
       <c r="R40" t="n">
-        <v>32.7</v>
+        <v>19</v>
       </c>
       <c r="S40" t="n">
-        <v>-25</v>
+        <v>7</v>
       </c>
       <c r="T40" t="n">
-        <v>71</v>
+        <v>4158</v>
       </c>
       <c r="U40" t="n">
-        <v>-11</v>
+        <v>44</v>
       </c>
       <c r="V40" t="n">
-        <v>1.48</v>
+        <v>25.89</v>
       </c>
       <c r="W40" t="n">
-        <v>10.7</v>
+        <v>53.4</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="Y40" t="b">
         <v>1</v>
       </c>
       <c r="Z40" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="AA40" t="n">
-        <v>109.5</v>
+        <v>1282.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>112.05</v>
+        <v>1380.71</v>
       </c>
       <c r="AC40" t="n">
-        <v>27.3</v>
+        <v>-11.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>105.19</v>
+        <v>1104.337889591841</v>
       </c>
       <c r="AE40" t="n">
-        <v>20.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
@@ -7777,22 +7775,22 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AM40" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -7807,7 +7805,7 @@
         <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
@@ -7822,7 +7820,7 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>78892500</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
         <v>0</v>
@@ -7895,13 +7893,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="Q41" t="n">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="R41" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
@@ -8017,27 +8015,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
         <v>17</v>
@@ -8046,146 +8044,148 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>592.2</v>
+        <v>126.87</v>
       </c>
       <c r="J42" t="n">
-        <v>593.39</v>
+        <v>105.19</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.2</v>
+        <v>20.6</v>
       </c>
       <c r="L42" t="n">
-        <v>74.02</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>0.21</v>
+        <v>2.63</v>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.022</v>
+        <v>0.052</v>
       </c>
       <c r="Q42" t="n">
-        <v>941</v>
-      </c>
-      <c r="R42" t="inlineStr"/>
+        <v>5034</v>
+      </c>
+      <c r="R42" t="n">
+        <v>32.8</v>
+      </c>
       <c r="S42" t="n">
-        <v>-2</v>
+        <v>-25</v>
       </c>
       <c r="T42" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="U42" t="n">
-        <v>-152</v>
+        <v>-11</v>
       </c>
       <c r="V42" t="n">
-        <v>-6.5</v>
+        <v>1.48</v>
       </c>
       <c r="W42" t="n">
-        <v>9.24</v>
+        <v>10.7</v>
       </c>
       <c r="X42" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="AA42" t="n">
-        <v>590.46</v>
+        <v>109.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>545.01</v>
+        <v>112.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>17.9</v>
+        <v>27.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>593.3866666666667</v>
+        <v>105.19</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.2</v>
+        <v>20.6</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="n">
         <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS42" t="n">
         <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>966192</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>2136192</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2136192</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2136192</v>
+        <v>78892500</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>2136192</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA42" t="n">
         <v>0</v>
@@ -8249,13 +8249,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.271</v>
+        <v>2.27</v>
       </c>
       <c r="Q43" t="n">
-        <v>24551</v>
+        <v>24554</v>
       </c>
       <c r="R43" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="S43" t="n">
         <v>-2</v>
@@ -8431,13 +8431,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.166</v>
+        <v>0.169</v>
       </c>
       <c r="Q44" t="n">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="R44" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="S44" t="n">
         <v>185</v>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
       <c r="Q46" t="n">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="R46" t="n">
         <v>13.8</v>
@@ -8973,13 +8973,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="Q47" t="n">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="R47" t="n">
-        <v>50.1</v>
+        <v>49.2</v>
       </c>
       <c r="S47" t="n">
         <v>7</v>
@@ -9158,10 +9158,10 @@
         <v>0.035</v>
       </c>
       <c r="Q48" t="n">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="R48" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="S48" t="n">
         <v>17</v>
@@ -9337,13 +9337,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.191</v>
+        <v>0.194</v>
       </c>
       <c r="Q49" t="n">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="R49" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S49" t="n">
         <v>19</v>
@@ -9519,10 +9519,10 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.29</v>
+        <v>0.289</v>
       </c>
       <c r="Q50" t="n">
-        <v>3529</v>
+        <v>3533</v>
       </c>
       <c r="R50" t="n">
         <v>24.7</v>
@@ -9704,10 +9704,10 @@
         <v>0.052</v>
       </c>
       <c r="Q51" t="n">
-        <v>9076</v>
+        <v>9008</v>
       </c>
       <c r="R51" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="S51" t="n">
         <v>21</v>
@@ -9886,10 +9886,10 @@
         <v>0.008</v>
       </c>
       <c r="Q52" t="n">
-        <v>112322</v>
+        <v>112251</v>
       </c>
       <c r="R52" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="S52" t="n">
         <v>18</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.248</v>
+        <v>0.244</v>
       </c>
       <c r="Q53" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="R53" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="S53" t="n">
         <v>16</v>
@@ -10247,13 +10247,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="Q54" t="n">
-        <v>1738</v>
+        <v>1730</v>
       </c>
       <c r="R54" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="S54" t="n">
         <v>39</v>
@@ -10429,13 +10429,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="Q55" t="n">
-        <v>1486</v>
+        <v>1500</v>
       </c>
       <c r="R55" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="S55" t="n">
         <v>13</v>
@@ -10611,13 +10611,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>907</v>
+        <v>935</v>
       </c>
       <c r="R56" t="n">
-        <v>24.7</v>
+        <v>25.5</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -12073,105 +12073,105 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>207.79</v>
+        <v>592.2</v>
       </c>
       <c r="D38" t="n">
-        <v>210.84</v>
+        <v>593.62</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F38" t="n">
-        <v>67.04000000000001</v>
+        <v>74.02</v>
       </c>
       <c r="G38" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1206.1</v>
+        <v>207.79</v>
       </c>
       <c r="D39" t="n">
-        <v>1104.34</v>
+        <v>210.84</v>
       </c>
       <c r="E39" t="n">
-        <v>9.199999999999999</v>
+        <v>-1.4</v>
       </c>
       <c r="F39" t="n">
-        <v>60.82</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>5.22</v>
+        <v>0.42</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>126.87</v>
+        <v>1206.1</v>
       </c>
       <c r="D40" t="n">
-        <v>105.19</v>
+        <v>1104.34</v>
       </c>
       <c r="E40" t="n">
-        <v>20.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>67.15000000000001</v>
+        <v>60.82</v>
       </c>
       <c r="G40" t="n">
-        <v>2.63</v>
+        <v>5.22</v>
       </c>
       <c r="H40" t="n">
         <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
@@ -12213,35 +12213,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>592.2</v>
+        <v>126.87</v>
       </c>
       <c r="D42" t="n">
-        <v>593.39</v>
+        <v>105.19</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.2</v>
+        <v>20.6</v>
       </c>
       <c r="F42" t="n">
-        <v>74.02</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>0.21</v>
+        <v>2.63</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">

--- a/output/2026-09-15/enriched_analysis.xlsx
+++ b/output/2026-09-15/enriched_analysis.xlsx
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.653</v>
+        <v>3.609</v>
       </c>
       <c r="Q2" t="n">
-        <v>2899</v>
+        <v>2935</v>
       </c>
       <c r="R2" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Q3" t="n">
-        <v>2691</v>
+        <v>2643</v>
       </c>
       <c r="R3" t="n">
-        <v>9.27</v>
+        <v>9.07</v>
       </c>
       <c r="S3" t="n">
         <v>36</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="Q4" t="n">
-        <v>2342</v>
+        <v>2307</v>
       </c>
       <c r="R4" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="S4" t="n">
         <v>-3</v>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="R5" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="S5" t="n">
         <v>22</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.803</v>
+        <v>2.843</v>
       </c>
       <c r="Q7" t="n">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="R7" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.061</v>
+        <v>0.057</v>
       </c>
       <c r="Q8" t="n">
-        <v>1343</v>
+        <v>1430</v>
       </c>
       <c r="R8" t="n">
-        <v>18.1</v>
+        <v>19.3</v>
       </c>
       <c r="S8" t="n">
         <v>55</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.645</v>
+        <v>0.649</v>
       </c>
       <c r="Q9" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.324</v>
+        <v>0.321</v>
       </c>
       <c r="Q10" t="n">
-        <v>2617</v>
+        <v>2642</v>
       </c>
       <c r="R10" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.285</v>
+        <v>2.228</v>
       </c>
       <c r="Q11" t="n">
-        <v>2608</v>
+        <v>2674</v>
       </c>
       <c r="R11" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="S11" t="n">
         <v>6</v>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.046</v>
+        <v>0.047</v>
       </c>
       <c r="Q12" t="n">
-        <v>15611</v>
+        <v>15491</v>
       </c>
       <c r="R12" t="n">
-        <v>39.7</v>
+        <v>39.4</v>
       </c>
       <c r="S12" t="n">
         <v>83</v>
@@ -2816,10 +2816,10 @@
         <v>0.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="R13" t="n">
-        <v>61.8</v>
+        <v>62</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2998,7 +2998,7 @@
         <v>0.006</v>
       </c>
       <c r="Q14" t="n">
-        <v>4263</v>
+        <v>4266</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
@@ -3175,13 +3175,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.194</v>
+        <v>0.188</v>
       </c>
       <c r="Q15" t="n">
-        <v>890</v>
+        <v>921</v>
       </c>
       <c r="R15" t="n">
-        <v>8.74</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S15" t="n">
         <v>7</v>
@@ -3360,10 +3360,10 @@
         <v>0.013</v>
       </c>
       <c r="Q16" t="n">
-        <v>16130</v>
+        <v>16399</v>
       </c>
       <c r="R16" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="S16" t="n">
         <v>16</v>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.411</v>
+        <v>0.414</v>
       </c>
       <c r="Q17" t="n">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="R17" t="n">
-        <v>56</v>
+        <v>55.6</v>
       </c>
       <c r="S17" t="n">
         <v>21</v>
@@ -3727,7 +3727,7 @@
         <v>395</v>
       </c>
       <c r="R18" t="n">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="S18" t="n">
         <v>-61</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.7</v>
+        <v>1.585</v>
       </c>
       <c r="Q19" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.095</v>
+        <v>0.098</v>
       </c>
       <c r="Q20" t="n">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="R20" t="n">
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
       <c r="S20" t="n">
         <v>24</v>
@@ -4103,7 +4103,7 @@
         <v>4.96</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="Q21" t="n">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="R21" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S21" t="n">
         <v>-8</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="Q22" t="n">
-        <v>1574</v>
+        <v>1611</v>
       </c>
       <c r="R22" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="S22" t="n">
         <v>581</v>
@@ -4623,13 +4623,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.081</v>
+        <v>1.077</v>
       </c>
       <c r="Q23" t="n">
-        <v>9503</v>
+        <v>9536</v>
       </c>
       <c r="R23" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S23" t="n">
         <v>-12</v>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="Q24" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R24" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="S24" t="n">
         <v>118</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.198</v>
+        <v>0.197</v>
       </c>
       <c r="Q25" t="n">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="R25" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="S25" t="n">
         <v>19</v>
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="Q26" t="n">
-        <v>1986</v>
+        <v>1966</v>
       </c>
       <c r="R26" t="n">
-        <v>45.6</v>
+        <v>45.1</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -5350,10 +5350,10 @@
         <v>0.038</v>
       </c>
       <c r="Q27" t="n">
-        <v>3529</v>
+        <v>3513</v>
       </c>
       <c r="R27" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="S27" t="n">
         <v>-4</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.422</v>
+        <v>0.414</v>
       </c>
       <c r="Q28" t="n">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="R28" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="S28" t="n">
         <v>21</v>
@@ -5714,10 +5714,10 @@
         <v>0.007</v>
       </c>
       <c r="Q29" t="n">
-        <v>5640</v>
+        <v>5587</v>
       </c>
       <c r="R29" t="n">
-        <v>9.529999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="S29" t="n">
         <v>43</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.507</v>
+        <v>0.504</v>
       </c>
       <c r="Q31" t="n">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="R31" t="n">
         <v>14.8</v>
@@ -6257,13 +6257,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.598</v>
+        <v>0.599</v>
       </c>
       <c r="Q32" t="n">
-        <v>2281</v>
+        <v>2276</v>
       </c>
       <c r="R32" t="n">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -6439,13 +6439,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.271</v>
+        <v>0.273</v>
       </c>
       <c r="Q33" t="n">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="R33" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="S33" t="n">
         <v>12</v>
@@ -6624,10 +6624,10 @@
         <v>0.046</v>
       </c>
       <c r="Q34" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="R34" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.396</v>
+        <v>0.398</v>
       </c>
       <c r="Q35" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="R35" t="n">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="S35" t="n">
         <v>246</v>
@@ -6985,13 +6985,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.097</v>
+        <v>0.098</v>
       </c>
       <c r="Q36" t="n">
-        <v>1530</v>
+        <v>1517</v>
       </c>
       <c r="R36" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="S36" t="n">
         <v>6</v>
@@ -7170,10 +7170,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>53053</v>
+        <v>52593</v>
       </c>
       <c r="R37" t="n">
-        <v>45</v>
+        <v>44.6</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="Q38" t="n">
-        <v>928</v>
+        <v>944</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
@@ -7714,10 +7714,10 @@
         <v>0.002</v>
       </c>
       <c r="Q40" t="n">
-        <v>346752</v>
+        <v>343984</v>
       </c>
       <c r="R40" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="Q41" t="n">
-        <v>835</v>
+        <v>817</v>
       </c>
       <c r="R41" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
@@ -8070,7 +8070,7 @@
         <v>0.052</v>
       </c>
       <c r="Q42" t="n">
-        <v>5034</v>
+        <v>5024</v>
       </c>
       <c r="R42" t="n">
         <v>32.8</v>
@@ -8249,13 +8249,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.27</v>
+        <v>2.278</v>
       </c>
       <c r="Q43" t="n">
-        <v>24554</v>
+        <v>24475</v>
       </c>
       <c r="R43" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="S43" t="n">
         <v>-2</v>
@@ -8431,13 +8431,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.169</v>
+        <v>0.171</v>
       </c>
       <c r="Q44" t="n">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="R44" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="S44" t="n">
         <v>185</v>
@@ -8559,12 +8559,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -8579,84 +8579,82 @@
         <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>25.59</v>
+        <v>171.54</v>
       </c>
       <c r="J45" t="n">
-        <v>29.77</v>
+        <v>182.69</v>
       </c>
       <c r="K45" t="n">
-        <v>-14</v>
+        <v>-6.1</v>
       </c>
       <c r="L45" t="n">
-        <v>69.03</v>
+        <v>69.05</v>
       </c>
       <c r="M45" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>575</v>
+      </c>
+      <c r="R45" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="S45" t="n">
+        <v>61</v>
+      </c>
+      <c r="T45" t="n">
+        <v>15</v>
+      </c>
+      <c r="U45" t="n">
+        <v>82</v>
+      </c>
+      <c r="V45" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="W45" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="X45" t="n">
         <v>0.35</v>
       </c>
-      <c r="N45" t="n">
-        <v>7</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>103</v>
-      </c>
-      <c r="R45" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="S45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>26</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="W45" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
       <c r="Y45" t="b">
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>21.51</v>
+        <v>12</v>
       </c>
       <c r="AA45" t="n">
-        <v>27.13</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>24.71</v>
-      </c>
+        <v>169.73</v>
+      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>29</v>
+        <v>-11.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>29.69418572675427</v>
+        <v>182.6945759634963</v>
       </c>
       <c r="AE45" t="n">
-        <v>-13.8</v>
+        <v>-6.1</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -8675,22 +8673,22 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -8705,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AS45" t="n">
         <v>0</v>
@@ -8720,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>2451267</v>
+        <v>7447179</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
@@ -8729,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA45" t="n">
         <v>0</v>
@@ -8741,16 +8739,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -8758,85 +8756,87 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
+        <v>23</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>490.25</v>
+      </c>
+      <c r="J46" t="n">
+        <v>545.03</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3090</v>
+      </c>
+      <c r="R46" t="n">
+        <v>21</v>
+      </c>
+      <c r="S46" t="n">
         <v>17</v>
       </c>
-      <c r="G46" t="n">
-        <v>4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>171.54</v>
-      </c>
-      <c r="J46" t="n">
-        <v>182.69</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>580</v>
-      </c>
-      <c r="R46" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="S46" t="n">
-        <v>61</v>
-      </c>
       <c r="T46" t="n">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="U46" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="V46" t="n">
-        <v>3.07</v>
+        <v>3.73</v>
       </c>
       <c r="W46" t="n">
-        <v>42.7</v>
+        <v>19.8</v>
       </c>
       <c r="X46" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="Y46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AA46" t="n">
-        <v>169.73</v>
-      </c>
-      <c r="AB46" t="inlineStr"/>
+        <v>521.58</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>554.23</v>
+      </c>
       <c r="AC46" t="n">
-        <v>-11.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>182.6945759634963</v>
+        <v>545.03455</v>
       </c>
       <c r="AE46" t="n">
-        <v>-6.1</v>
+        <v>-10.1</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -8855,22 +8855,22 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AK46" t="n">
         <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AM46" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>7447179</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
@@ -8909,7 +8909,7 @@
         <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA46" t="n">
         <v>0</v>
@@ -9103,16 +9103,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -9120,121 +9120,121 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I48" t="n">
-        <v>490.25</v>
+        <v>54.05</v>
       </c>
       <c r="J48" t="n">
-        <v>545.03</v>
+        <v>60.15</v>
       </c>
       <c r="K48" t="n">
         <v>-10.1</v>
       </c>
       <c r="L48" t="n">
-        <v>69.90000000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.035</v>
+        <v>0.196</v>
       </c>
       <c r="Q48" t="n">
-        <v>3091</v>
+        <v>460</v>
       </c>
       <c r="R48" t="n">
-        <v>20.9</v>
+        <v>11.5</v>
       </c>
       <c r="S48" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T48" t="n">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="U48" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="V48" t="n">
-        <v>3.73</v>
+        <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>19.8</v>
+        <v>12</v>
       </c>
       <c r="X48" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="Y48" t="b">
         <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>40</v>
+        <v>3.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>521.58</v>
+        <v>57.31</v>
       </c>
       <c r="AB48" t="n">
-        <v>554.23</v>
+        <v>58.62</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.6</v>
+        <v>-4.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>545.03455</v>
+        <v>60.1322085106383</v>
       </c>
       <c r="AE48" t="n">
         <v>-10.1</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL48" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="AM48" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
@@ -9246,10 +9246,10 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS48" t="n">
         <v>0</v>
@@ -9261,10 +9261,10 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>14131069</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>14131069</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
@@ -9285,12 +9285,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -9302,121 +9302,117 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H49" t="n">
         <v>-1</v>
       </c>
       <c r="I49" t="n">
-        <v>54.05</v>
+        <v>25.59</v>
       </c>
       <c r="J49" t="n">
-        <v>60.15</v>
+        <v>29.77</v>
       </c>
       <c r="K49" t="n">
-        <v>-10.1</v>
+        <v>-14</v>
       </c>
       <c r="L49" t="n">
-        <v>73.01000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="M49" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>464</v>
-      </c>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
-        <v>11.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="S49" t="n">
-        <v>19</v>
+        <v>-1</v>
       </c>
       <c r="T49" t="n">
-        <v>21</v>
+        <v>0.4</v>
       </c>
       <c r="U49" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="V49" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="W49" t="n">
-        <v>12</v>
+        <v>-0.18</v>
       </c>
       <c r="X49" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.4</v>
+        <v>21.51</v>
       </c>
       <c r="AA49" t="n">
-        <v>57.31</v>
+        <v>27.13</v>
       </c>
       <c r="AB49" t="n">
-        <v>58.62</v>
+        <v>24.71</v>
       </c>
       <c r="AC49" t="n">
-        <v>-4.8</v>
+        <v>29</v>
       </c>
       <c r="AD49" t="n">
-        <v>60.1322085106383</v>
+        <v>29.69418572675427</v>
       </c>
       <c r="AE49" t="n">
-        <v>-10.1</v>
+        <v>-13.8</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AK49" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AL49" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="AM49" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -9428,10 +9424,10 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AS49" t="n">
         <v>0</v>
@@ -9443,10 +9439,10 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>14131069</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>14131069</v>
+        <v>2451267</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
@@ -9519,13 +9515,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.289</v>
+        <v>0.294</v>
       </c>
       <c r="Q50" t="n">
-        <v>3533</v>
+        <v>3482</v>
       </c>
       <c r="R50" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="S50" t="n">
         <v>2</v>
@@ -9701,13 +9697,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="Q51" t="n">
-        <v>9008</v>
+        <v>8901</v>
       </c>
       <c r="R51" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="S51" t="n">
         <v>21</v>
@@ -10065,13 +10061,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.244</v>
+        <v>0.246</v>
       </c>
       <c r="Q53" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="R53" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="S53" t="n">
         <v>16</v>
@@ -10247,13 +10243,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="Q54" t="n">
-        <v>1730</v>
+        <v>1735</v>
       </c>
       <c r="R54" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="S54" t="n">
         <v>39</v>
@@ -10429,13 +10425,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="Q55" t="n">
-        <v>1500</v>
+        <v>1493</v>
       </c>
       <c r="R55" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="S55" t="n">
         <v>13</v>
@@ -10614,7 +10610,7 @@
         <v>0.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="R56" t="n">
         <v>25.5</v>
@@ -11518,7 +11514,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -12318,70 +12314,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>25.59</v>
+        <v>171.54</v>
       </c>
       <c r="D45" t="n">
-        <v>29.77</v>
+        <v>182.69</v>
       </c>
       <c r="E45" t="n">
-        <v>-14</v>
+        <v>-6.1</v>
       </c>
       <c r="F45" t="n">
-        <v>69.03</v>
+        <v>69.05</v>
       </c>
       <c r="G45" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>171.54</v>
+        <v>490.25</v>
       </c>
       <c r="D46" t="n">
-        <v>182.69</v>
+        <v>545.03</v>
       </c>
       <c r="E46" t="n">
-        <v>-6.1</v>
+        <v>-10.1</v>
       </c>
       <c r="F46" t="n">
-        <v>69.05</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
@@ -12423,70 +12419,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>490.25</v>
+        <v>54.05</v>
       </c>
       <c r="D48" t="n">
-        <v>545.03</v>
+        <v>60.15</v>
       </c>
       <c r="E48" t="n">
         <v>-10.1</v>
       </c>
       <c r="F48" t="n">
-        <v>69.90000000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>54.05</v>
+        <v>25.59</v>
       </c>
       <c r="D49" t="n">
-        <v>60.15</v>
+        <v>29.77</v>
       </c>
       <c r="E49" t="n">
-        <v>-10.1</v>
+        <v>-14</v>
       </c>
       <c r="F49" t="n">
-        <v>73.01000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-15/enriched_analysis.xlsx
+++ b/output/2026-09-15/enriched_analysis.xlsx
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.609</v>
+        <v>3.625</v>
       </c>
       <c r="Q2" t="n">
-        <v>2935</v>
+        <v>2922</v>
       </c>
       <c r="R2" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -998,10 +998,10 @@
         <v>0.081</v>
       </c>
       <c r="Q3" t="n">
-        <v>2643</v>
+        <v>2623</v>
       </c>
       <c r="R3" t="n">
-        <v>9.07</v>
+        <v>9.02</v>
       </c>
       <c r="S3" t="n">
         <v>36</v>
@@ -1180,7 +1180,7 @@
         <v>0.136</v>
       </c>
       <c r="Q4" t="n">
-        <v>2307</v>
+        <v>2311</v>
       </c>
       <c r="R4" t="n">
         <v>20.2</v>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.57</v>
+        <v>0.571</v>
       </c>
       <c r="Q5" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="R5" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S5" t="n">
         <v>22</v>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.877</v>
+        <v>0.898</v>
       </c>
       <c r="Q6" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="R6" t="n">
-        <v>8.970000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="S6" t="n">
         <v>17</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.843</v>
+        <v>2.855</v>
       </c>
       <c r="Q7" t="n">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="R7" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.057</v>
+        <v>0.059</v>
       </c>
       <c r="Q8" t="n">
-        <v>1430</v>
+        <v>1389</v>
       </c>
       <c r="R8" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="S8" t="n">
         <v>55</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.649</v>
+        <v>0.645</v>
       </c>
       <c r="Q9" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.321</v>
+        <v>0.325</v>
       </c>
       <c r="Q10" t="n">
-        <v>2642</v>
+        <v>2610</v>
       </c>
       <c r="R10" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -2634,10 +2634,10 @@
         <v>0.047</v>
       </c>
       <c r="Q12" t="n">
-        <v>15491</v>
+        <v>15395</v>
       </c>
       <c r="R12" t="n">
-        <v>39.4</v>
+        <v>39.2</v>
       </c>
       <c r="S12" t="n">
         <v>83</v>
@@ -2998,7 +2998,7 @@
         <v>0.006</v>
       </c>
       <c r="Q14" t="n">
-        <v>4266</v>
+        <v>4207</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
@@ -3360,10 +3360,10 @@
         <v>0.013</v>
       </c>
       <c r="Q16" t="n">
-        <v>16399</v>
+        <v>16276</v>
       </c>
       <c r="R16" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="S16" t="n">
         <v>16</v>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.414</v>
+        <v>0.417</v>
       </c>
       <c r="Q17" t="n">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="R17" t="n">
-        <v>55.6</v>
+        <v>55.3</v>
       </c>
       <c r="S17" t="n">
         <v>21</v>
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.532</v>
+        <v>0.534</v>
       </c>
       <c r="Q18" t="n">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="R18" t="n">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="S18" t="n">
         <v>-61</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.585</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>1611</v>
+        <v>1587</v>
       </c>
       <c r="R22" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="S22" t="n">
         <v>581</v>
@@ -4623,13 +4623,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.077</v>
+        <v>1.087</v>
       </c>
       <c r="Q23" t="n">
-        <v>9536</v>
+        <v>9450</v>
       </c>
       <c r="R23" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="S23" t="n">
         <v>-12</v>
@@ -4808,10 +4808,10 @@
         <v>0.133</v>
       </c>
       <c r="Q24" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R24" t="n">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="S24" t="n">
         <v>118</v>
@@ -4986,10 +4986,10 @@
         <v>0.197</v>
       </c>
       <c r="Q25" t="n">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="R25" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="S25" t="n">
         <v>19</v>
@@ -5168,10 +5168,10 @@
         <v>0.056</v>
       </c>
       <c r="Q26" t="n">
-        <v>1966</v>
+        <v>1947</v>
       </c>
       <c r="R26" t="n">
-        <v>45.1</v>
+        <v>44.7</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -5350,10 +5350,10 @@
         <v>0.038</v>
       </c>
       <c r="Q27" t="n">
-        <v>3513</v>
+        <v>3490</v>
       </c>
       <c r="R27" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="S27" t="n">
         <v>-4</v>
@@ -5714,10 +5714,10 @@
         <v>0.007</v>
       </c>
       <c r="Q29" t="n">
-        <v>5587</v>
+        <v>5556</v>
       </c>
       <c r="R29" t="n">
-        <v>9.44</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>43</v>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.201</v>
+        <v>0.202</v>
       </c>
       <c r="Q30" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R30" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="S30" t="n">
         <v>21</v>
@@ -6075,13 +6075,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.504</v>
+        <v>0.51</v>
       </c>
       <c r="Q31" t="n">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="R31" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="S31" t="n">
         <v>-1</v>
@@ -6260,10 +6260,10 @@
         <v>0.599</v>
       </c>
       <c r="Q32" t="n">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="R32" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.273</v>
+        <v>0.274</v>
       </c>
       <c r="Q33" t="n">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="R33" t="n">
         <v>19.3</v>
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.398</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="R35" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S35" t="n">
         <v>246</v>
@@ -6988,7 +6988,7 @@
         <v>0.098</v>
       </c>
       <c r="Q36" t="n">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="R36" t="n">
         <v>13.7</v>
@@ -7170,10 +7170,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>52593</v>
+        <v>52528</v>
       </c>
       <c r="R37" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -7714,7 +7714,7 @@
         <v>0.002</v>
       </c>
       <c r="Q40" t="n">
-        <v>343984</v>
+        <v>343279</v>
       </c>
       <c r="R40" t="n">
         <v>18.8</v>
@@ -7896,10 +7896,10 @@
         <v>0.038</v>
       </c>
       <c r="Q41" t="n">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="R41" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
@@ -8067,13 +8067,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="Q42" t="n">
-        <v>5024</v>
+        <v>5005</v>
       </c>
       <c r="R42" t="n">
-        <v>32.8</v>
+        <v>32.6</v>
       </c>
       <c r="S42" t="n">
         <v>-25</v>
@@ -8249,13 +8249,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.278</v>
+        <v>2.282</v>
       </c>
       <c r="Q43" t="n">
-        <v>24475</v>
+        <v>24423</v>
       </c>
       <c r="R43" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="S43" t="n">
         <v>-2</v>
@@ -8434,7 +8434,7 @@
         <v>0.171</v>
       </c>
       <c r="Q44" t="n">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="R44" t="n">
         <v>13.2</v>
@@ -8559,12 +8559,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -8579,117 +8579,119 @@
         <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I45" t="n">
-        <v>171.54</v>
+        <v>25.59</v>
       </c>
       <c r="J45" t="n">
-        <v>182.69</v>
+        <v>29.77</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.1</v>
+        <v>-14</v>
       </c>
       <c r="L45" t="n">
-        <v>69.05</v>
+        <v>69.03</v>
       </c>
       <c r="M45" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.129</v>
+        <v>0.34</v>
       </c>
       <c r="Q45" t="n">
-        <v>575</v>
+        <v>103</v>
       </c>
       <c r="R45" t="n">
-        <v>13.6</v>
+        <v>73.8</v>
       </c>
       <c r="S45" t="n">
-        <v>61</v>
+        <v>-1</v>
       </c>
       <c r="T45" t="n">
-        <v>15</v>
+        <v>0.4</v>
       </c>
       <c r="U45" t="n">
+        <v>26</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>29.69418572675427</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>91</v>
+      </c>
+      <c r="AM45" t="n">
         <v>82</v>
       </c>
-      <c r="V45" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="W45" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>169.73</v>
-      </c>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="n">
-        <v>-11.3</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>182.6945759634963</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>83</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>83</v>
-      </c>
       <c r="AN45" t="n">
         <v>0</v>
       </c>
@@ -8703,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AS45" t="n">
         <v>0</v>
@@ -8718,7 +8720,7 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>7447179</v>
+        <v>2451267</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
@@ -8727,7 +8729,7 @@
         <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA45" t="n">
         <v>0</v>
@@ -8739,16 +8741,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -8756,87 +8758,85 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>490.25</v>
+        <v>171.54</v>
       </c>
       <c r="J46" t="n">
-        <v>545.03</v>
+        <v>182.69</v>
       </c>
       <c r="K46" t="n">
-        <v>-10.1</v>
+        <v>-6.1</v>
       </c>
       <c r="L46" t="n">
-        <v>69.90000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="M46" t="n">
-        <v>1.09</v>
+        <v>0.74</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.035</v>
+        <v>0.127</v>
       </c>
       <c r="Q46" t="n">
-        <v>3090</v>
+        <v>581</v>
       </c>
       <c r="R46" t="n">
-        <v>21</v>
+        <v>13.8</v>
       </c>
       <c r="S46" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="T46" t="n">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="U46" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="V46" t="n">
-        <v>3.73</v>
+        <v>3.07</v>
       </c>
       <c r="W46" t="n">
-        <v>19.8</v>
+        <v>42.7</v>
       </c>
       <c r="X46" t="n">
-        <v>0.62</v>
+        <v>0.35</v>
       </c>
       <c r="Y46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AA46" t="n">
-        <v>521.58</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>554.23</v>
-      </c>
+        <v>169.73</v>
+      </c>
+      <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>-0.6</v>
+        <v>-11.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>545.03455</v>
+        <v>182.6945759634963</v>
       </c>
       <c r="AE46" t="n">
-        <v>-10.1</v>
+        <v>-6.1</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -8855,22 +8855,22 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AK46" t="n">
         <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS46" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>7447179</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
@@ -8909,7 +8909,7 @@
         <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA46" t="n">
         <v>0</v>
@@ -9103,138 +9103,138 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C48" t="n">
+        <v>24</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
         <v>23</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>5</v>
-      </c>
-      <c r="F48" t="n">
-        <v>19</v>
-      </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>54.05</v>
+        <v>490.25</v>
       </c>
       <c r="J48" t="n">
-        <v>60.15</v>
+        <v>545.03</v>
       </c>
       <c r="K48" t="n">
         <v>-10.1</v>
       </c>
       <c r="L48" t="n">
-        <v>73.01000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.196</v>
+        <v>0.036</v>
       </c>
       <c r="Q48" t="n">
-        <v>460</v>
+        <v>3063</v>
       </c>
       <c r="R48" t="n">
-        <v>11.5</v>
+        <v>20.8</v>
       </c>
       <c r="S48" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T48" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="U48" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="V48" t="n">
-        <v>1.22</v>
+        <v>3.73</v>
       </c>
       <c r="W48" t="n">
-        <v>12</v>
+        <v>19.8</v>
       </c>
       <c r="X48" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="Y48" t="b">
         <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.4</v>
+        <v>40</v>
       </c>
       <c r="AA48" t="n">
-        <v>57.31</v>
+        <v>521.58</v>
       </c>
       <c r="AB48" t="n">
-        <v>58.62</v>
+        <v>554.23</v>
       </c>
       <c r="AC48" t="n">
-        <v>-4.8</v>
+        <v>-0.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>60.1322085106383</v>
+        <v>545.03455</v>
       </c>
       <c r="AE48" t="n">
         <v>-10.1</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="AM48" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
@@ -9246,10 +9246,10 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
         <v>0</v>
@@ -9261,10 +9261,10 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>14131069</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>14131069</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
@@ -9285,12 +9285,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -9302,117 +9302,121 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>-1</v>
       </c>
       <c r="I49" t="n">
-        <v>25.59</v>
+        <v>54.05</v>
       </c>
       <c r="J49" t="n">
-        <v>29.77</v>
+        <v>60.15</v>
       </c>
       <c r="K49" t="n">
-        <v>-14</v>
+        <v>-10.1</v>
       </c>
       <c r="L49" t="n">
-        <v>69.03</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="N49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>460</v>
+      </c>
       <c r="R49" t="n">
-        <v>71.09999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="S49" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="T49" t="n">
-        <v>0.4</v>
+        <v>21</v>
       </c>
       <c r="U49" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="V49" t="n">
-        <v>0.59</v>
+        <v>1.22</v>
       </c>
       <c r="W49" t="n">
-        <v>-0.18</v>
+        <v>12</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="Y49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>21.51</v>
+        <v>3.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>27.13</v>
+        <v>57.31</v>
       </c>
       <c r="AB49" t="n">
-        <v>24.71</v>
+        <v>58.62</v>
       </c>
       <c r="AC49" t="n">
-        <v>29</v>
+        <v>-4.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>29.69418572675427</v>
+        <v>60.1322085106383</v>
       </c>
       <c r="AE49" t="n">
-        <v>-13.8</v>
+        <v>-10.1</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AK49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AL49" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="AM49" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -9424,10 +9428,10 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AS49" t="n">
         <v>0</v>
@@ -9439,10 +9443,10 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>14131069</v>
       </c>
       <c r="AW49" t="n">
-        <v>2451267</v>
+        <v>14131069</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
@@ -9518,7 +9522,7 @@
         <v>0.294</v>
       </c>
       <c r="Q50" t="n">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="R50" t="n">
         <v>24.4</v>
@@ -9700,10 +9704,10 @@
         <v>0.053</v>
       </c>
       <c r="Q51" t="n">
-        <v>8901</v>
+        <v>8857</v>
       </c>
       <c r="R51" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="S51" t="n">
         <v>21</v>
@@ -9882,7 +9886,7 @@
         <v>0.008</v>
       </c>
       <c r="Q52" t="n">
-        <v>112251</v>
+        <v>112261</v>
       </c>
       <c r="R52" t="n">
         <v>32.3</v>
@@ -10061,13 +10065,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.246</v>
+        <v>0.249</v>
       </c>
       <c r="Q53" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="R53" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="S53" t="n">
         <v>16</v>
@@ -10243,13 +10247,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.376</v>
+        <v>0.379</v>
       </c>
       <c r="Q54" t="n">
-        <v>1735</v>
+        <v>1724</v>
       </c>
       <c r="R54" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="S54" t="n">
         <v>39</v>
@@ -10428,10 +10432,10 @@
         <v>0.042</v>
       </c>
       <c r="Q55" t="n">
-        <v>1493</v>
+        <v>1482</v>
       </c>
       <c r="R55" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="S55" t="n">
         <v>13</v>
@@ -12314,70 +12318,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>171.54</v>
+        <v>25.59</v>
       </c>
       <c r="D45" t="n">
-        <v>182.69</v>
+        <v>29.77</v>
       </c>
       <c r="E45" t="n">
-        <v>-6.1</v>
+        <v>-14</v>
       </c>
       <c r="F45" t="n">
-        <v>69.05</v>
+        <v>69.03</v>
       </c>
       <c r="G45" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>490.25</v>
+        <v>171.54</v>
       </c>
       <c r="D46" t="n">
-        <v>545.03</v>
+        <v>182.69</v>
       </c>
       <c r="E46" t="n">
-        <v>-10.1</v>
+        <v>-6.1</v>
       </c>
       <c r="F46" t="n">
-        <v>69.90000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="G46" t="n">
-        <v>1.09</v>
+        <v>0.74</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
@@ -12419,70 +12423,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>54.05</v>
+        <v>490.25</v>
       </c>
       <c r="D48" t="n">
-        <v>60.15</v>
+        <v>545.03</v>
       </c>
       <c r="E48" t="n">
         <v>-10.1</v>
       </c>
       <c r="F48" t="n">
-        <v>73.01000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25.59</v>
+        <v>54.05</v>
       </c>
       <c r="D49" t="n">
-        <v>29.77</v>
+        <v>60.15</v>
       </c>
       <c r="E49" t="n">
-        <v>-14</v>
+        <v>-10.1</v>
       </c>
       <c r="F49" t="n">
-        <v>69.03</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-15/enriched_analysis.xlsx
+++ b/output/2026-09-15/enriched_analysis.xlsx
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.625</v>
+        <v>3.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2922</v>
+        <v>2894</v>
       </c>
       <c r="R2" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.081</v>
+        <v>0.083</v>
       </c>
       <c r="Q3" t="n">
-        <v>2623</v>
+        <v>2573</v>
       </c>
       <c r="R3" t="n">
-        <v>9.02</v>
+        <v>8.82</v>
       </c>
       <c r="S3" t="n">
         <v>36</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.136</v>
+        <v>0.144</v>
       </c>
       <c r="Q4" t="n">
-        <v>2311</v>
+        <v>2184</v>
       </c>
       <c r="R4" t="n">
-        <v>20.2</v>
+        <v>19.1</v>
       </c>
       <c r="S4" t="n">
         <v>-3</v>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.571</v>
+        <v>0.575</v>
       </c>
       <c r="Q5" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="R5" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S5" t="n">
         <v>22</v>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.898</v>
+        <v>0.877</v>
       </c>
       <c r="Q6" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="R6" t="n">
-        <v>8.77</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="S6" t="n">
         <v>17</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.855</v>
+        <v>2.866</v>
       </c>
       <c r="Q7" t="n">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="R7" t="n">
         <v>11.4</v>
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1389</v>
+        <v>1366</v>
       </c>
       <c r="R8" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="S8" t="n">
         <v>55</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.645</v>
+        <v>0.661</v>
       </c>
       <c r="Q9" t="n">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.325</v>
+        <v>0.329</v>
       </c>
       <c r="Q10" t="n">
-        <v>2610</v>
+        <v>2583</v>
       </c>
       <c r="R10" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -2634,10 +2634,10 @@
         <v>0.047</v>
       </c>
       <c r="Q12" t="n">
-        <v>15395</v>
+        <v>15373</v>
       </c>
       <c r="R12" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="S12" t="n">
         <v>83</v>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>25</v>
       </c>
       <c r="H13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>262.2</v>
@@ -2813,13 +2813,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.15</v>
+        <v>0.156</v>
       </c>
       <c r="Q13" t="n">
-        <v>742</v>
+        <v>713</v>
       </c>
       <c r="R13" t="n">
-        <v>62</v>
+        <v>59.6</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -3175,13 +3175,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.188</v>
+        <v>0.204</v>
       </c>
       <c r="Q15" t="n">
-        <v>921</v>
+        <v>850</v>
       </c>
       <c r="R15" t="n">
-        <v>9.050000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="S15" t="n">
         <v>7</v>
@@ -3360,10 +3360,10 @@
         <v>0.013</v>
       </c>
       <c r="Q16" t="n">
-        <v>16276</v>
+        <v>16205</v>
       </c>
       <c r="R16" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="S16" t="n">
         <v>16</v>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.417</v>
+        <v>0.407</v>
       </c>
       <c r="Q17" t="n">
-        <v>1085</v>
+        <v>1111</v>
       </c>
       <c r="R17" t="n">
-        <v>55.3</v>
+        <v>56.6</v>
       </c>
       <c r="S17" t="n">
         <v>21</v>
@@ -3727,7 +3727,7 @@
         <v>393</v>
       </c>
       <c r="R18" t="n">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="S18" t="n">
         <v>-61</v>
@@ -4082,10 +4082,10 @@
         <v>0.098</v>
       </c>
       <c r="Q20" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="R20" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="S20" t="n">
         <v>24</v>
@@ -4264,10 +4264,10 @@
         <v>0.081</v>
       </c>
       <c r="Q21" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="R21" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S21" t="n">
         <v>-8</v>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="Q22" t="n">
-        <v>1587</v>
+        <v>1576</v>
       </c>
       <c r="R22" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="S22" t="n">
         <v>581</v>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.087</v>
+        <v>1.089</v>
       </c>
       <c r="Q23" t="n">
-        <v>9450</v>
+        <v>9433</v>
       </c>
       <c r="R23" t="n">
         <v>12.4</v>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.133</v>
+        <v>0.135</v>
       </c>
       <c r="Q24" t="n">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="R24" t="n">
-        <v>6.06</v>
+        <v>5.99</v>
       </c>
       <c r="S24" t="n">
         <v>118</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.197</v>
+        <v>0.199</v>
       </c>
       <c r="Q25" t="n">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="R25" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="S25" t="n">
         <v>19</v>
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="Q26" t="n">
-        <v>1947</v>
+        <v>1891</v>
       </c>
       <c r="R26" t="n">
-        <v>44.7</v>
+        <v>43.4</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -5350,7 +5350,7 @@
         <v>0.038</v>
       </c>
       <c r="Q27" t="n">
-        <v>3490</v>
+        <v>3483</v>
       </c>
       <c r="R27" t="n">
         <v>20.6</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.414</v>
+        <v>0.427</v>
       </c>
       <c r="Q28" t="n">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="R28" t="n">
-        <v>38.6</v>
+        <v>37.4</v>
       </c>
       <c r="S28" t="n">
         <v>21</v>
@@ -5714,10 +5714,10 @@
         <v>0.007</v>
       </c>
       <c r="Q29" t="n">
-        <v>5556</v>
+        <v>5508</v>
       </c>
       <c r="R29" t="n">
-        <v>9.359999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="S29" t="n">
         <v>43</v>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.202</v>
+        <v>0.205</v>
       </c>
       <c r="Q30" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R30" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="S30" t="n">
         <v>21</v>
@@ -6075,13 +6075,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.51</v>
+        <v>0.511</v>
       </c>
       <c r="Q31" t="n">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="R31" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="S31" t="n">
         <v>-1</v>
@@ -6439,13 +6439,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.274</v>
+        <v>0.276</v>
       </c>
       <c r="Q33" t="n">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="R33" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="S33" t="n">
         <v>12</v>
@@ -6621,13 +6621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="Q34" t="n">
-        <v>905</v>
+        <v>928</v>
       </c>
       <c r="R34" t="n">
-        <v>96.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="Q35" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="R35" t="n">
-        <v>99.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="S35" t="n">
         <v>246</v>
@@ -6988,10 +6988,10 @@
         <v>0.098</v>
       </c>
       <c r="Q36" t="n">
-        <v>1512</v>
+        <v>1505</v>
       </c>
       <c r="R36" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="S36" t="n">
         <v>6</v>
@@ -7170,10 +7170,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>52528</v>
+        <v>52208</v>
       </c>
       <c r="R37" t="n">
-        <v>44.5</v>
+        <v>44.2</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="Q38" t="n">
-        <v>944</v>
+        <v>917</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
@@ -7714,10 +7714,10 @@
         <v>0.002</v>
       </c>
       <c r="Q40" t="n">
-        <v>343279</v>
+        <v>341379</v>
       </c>
       <c r="R40" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="Q41" t="n">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="R41" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
@@ -8067,13 +8067,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="Q42" t="n">
-        <v>5005</v>
+        <v>5064</v>
       </c>
       <c r="R42" t="n">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="S42" t="n">
         <v>-25</v>
@@ -8249,13 +8249,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.282</v>
+        <v>2.29</v>
       </c>
       <c r="Q43" t="n">
-        <v>24423</v>
+        <v>24341</v>
       </c>
       <c r="R43" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="S43" t="n">
         <v>-2</v>
@@ -8431,13 +8431,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.171</v>
+        <v>0.172</v>
       </c>
       <c r="Q44" t="n">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="R44" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S44" t="n">
         <v>185</v>
@@ -8559,12 +8559,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -8579,84 +8579,82 @@
         <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>25.59</v>
+        <v>171.54</v>
       </c>
       <c r="J45" t="n">
-        <v>29.77</v>
+        <v>182.69</v>
       </c>
       <c r="K45" t="n">
-        <v>-14</v>
+        <v>-6.1</v>
       </c>
       <c r="L45" t="n">
-        <v>69.03</v>
+        <v>69.05</v>
       </c>
       <c r="M45" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>583</v>
+      </c>
+      <c r="R45" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="S45" t="n">
+        <v>61</v>
+      </c>
+      <c r="T45" t="n">
+        <v>15</v>
+      </c>
+      <c r="U45" t="n">
+        <v>82</v>
+      </c>
+      <c r="V45" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="W45" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="X45" t="n">
         <v>0.35</v>
       </c>
-      <c r="N45" t="n">
-        <v>7</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>103</v>
-      </c>
-      <c r="R45" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="S45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>26</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="W45" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
       <c r="Y45" t="b">
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>21.51</v>
+        <v>12</v>
       </c>
       <c r="AA45" t="n">
-        <v>27.13</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>24.71</v>
-      </c>
+        <v>169.73</v>
+      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>29</v>
+        <v>-11.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>29.69418572675427</v>
+        <v>182.6945759634963</v>
       </c>
       <c r="AE45" t="n">
-        <v>-13.8</v>
+        <v>-6.1</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -8675,22 +8673,22 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -8705,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AS45" t="n">
         <v>0</v>
@@ -8720,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>2451267</v>
+        <v>7447179</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
@@ -8729,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA45" t="n">
         <v>0</v>
@@ -8741,16 +8739,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -8758,85 +8756,87 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
+        <v>23</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>490.25</v>
+      </c>
+      <c r="J46" t="n">
+        <v>545.03</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3046</v>
+      </c>
+      <c r="R46" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S46" t="n">
         <v>17</v>
       </c>
-      <c r="G46" t="n">
-        <v>4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>171.54</v>
-      </c>
-      <c r="J46" t="n">
-        <v>182.69</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>581</v>
-      </c>
-      <c r="R46" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="S46" t="n">
-        <v>61</v>
-      </c>
       <c r="T46" t="n">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="U46" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="V46" t="n">
-        <v>3.07</v>
+        <v>3.73</v>
       </c>
       <c r="W46" t="n">
-        <v>42.7</v>
+        <v>19.8</v>
       </c>
       <c r="X46" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="Y46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="AA46" t="n">
-        <v>169.73</v>
-      </c>
-      <c r="AB46" t="inlineStr"/>
+        <v>521.58</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>554.23</v>
+      </c>
       <c r="AC46" t="n">
-        <v>-11.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>182.6945759634963</v>
+        <v>545.03455</v>
       </c>
       <c r="AE46" t="n">
-        <v>-6.1</v>
+        <v>-10.1</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -8855,22 +8855,22 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AK46" t="n">
         <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AM46" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
         <v>0</v>
@@ -8900,7 +8900,7 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>7447179</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
@@ -8909,7 +8909,7 @@
         <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA46" t="n">
         <v>0</v>
@@ -8976,10 +8976,10 @@
         <v>0.041</v>
       </c>
       <c r="Q47" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="R47" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="S47" t="n">
         <v>7</v>
@@ -9103,16 +9103,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -9120,121 +9120,121 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I48" t="n">
-        <v>490.25</v>
+        <v>54.05</v>
       </c>
       <c r="J48" t="n">
-        <v>545.03</v>
+        <v>60.15</v>
       </c>
       <c r="K48" t="n">
         <v>-10.1</v>
       </c>
       <c r="L48" t="n">
-        <v>69.90000000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.036</v>
+        <v>0.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>3063</v>
+        <v>450</v>
       </c>
       <c r="R48" t="n">
-        <v>20.8</v>
+        <v>11.2</v>
       </c>
       <c r="S48" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T48" t="n">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="U48" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="V48" t="n">
-        <v>3.73</v>
+        <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>19.8</v>
+        <v>12</v>
       </c>
       <c r="X48" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="Y48" t="b">
         <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>40</v>
+        <v>3.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>521.58</v>
+        <v>57.31</v>
       </c>
       <c r="AB48" t="n">
-        <v>554.23</v>
+        <v>58.62</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.6</v>
+        <v>-4.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>545.03455</v>
+        <v>60.1322085106383</v>
       </c>
       <c r="AE48" t="n">
         <v>-10.1</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL48" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="AM48" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
@@ -9246,10 +9246,10 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS48" t="n">
         <v>0</v>
@@ -9261,10 +9261,10 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>14131069</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>14131069</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
@@ -9285,12 +9285,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -9302,121 +9302,117 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H49" t="n">
         <v>-1</v>
       </c>
       <c r="I49" t="n">
-        <v>54.05</v>
+        <v>25.59</v>
       </c>
       <c r="J49" t="n">
-        <v>60.15</v>
+        <v>29.77</v>
       </c>
       <c r="K49" t="n">
-        <v>-10.1</v>
+        <v>-14</v>
       </c>
       <c r="L49" t="n">
-        <v>73.01000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="M49" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>460</v>
-      </c>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
-        <v>11.5</v>
+        <v>70.2</v>
       </c>
       <c r="S49" t="n">
-        <v>19</v>
+        <v>-1</v>
       </c>
       <c r="T49" t="n">
-        <v>21</v>
+        <v>0.4</v>
       </c>
       <c r="U49" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="V49" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="W49" t="n">
-        <v>12</v>
+        <v>-0.18</v>
       </c>
       <c r="X49" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.4</v>
+        <v>21.51</v>
       </c>
       <c r="AA49" t="n">
-        <v>57.31</v>
+        <v>27.13</v>
       </c>
       <c r="AB49" t="n">
-        <v>58.62</v>
+        <v>24.71</v>
       </c>
       <c r="AC49" t="n">
-        <v>-4.8</v>
+        <v>29</v>
       </c>
       <c r="AD49" t="n">
-        <v>60.1322085106383</v>
+        <v>29.69418572675427</v>
       </c>
       <c r="AE49" t="n">
-        <v>-10.1</v>
+        <v>-13.8</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AK49" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AL49" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="AM49" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -9428,10 +9424,10 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AS49" t="n">
         <v>0</v>
@@ -9443,10 +9439,10 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>14131069</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>14131069</v>
+        <v>2451267</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
@@ -9522,10 +9518,10 @@
         <v>0.294</v>
       </c>
       <c r="Q50" t="n">
-        <v>3480</v>
+        <v>3473</v>
       </c>
       <c r="R50" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="S50" t="n">
         <v>2</v>
@@ -9704,10 +9700,10 @@
         <v>0.053</v>
       </c>
       <c r="Q51" t="n">
-        <v>8857</v>
+        <v>8886</v>
       </c>
       <c r="R51" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="S51" t="n">
         <v>21</v>
@@ -9886,10 +9882,10 @@
         <v>0.008</v>
       </c>
       <c r="Q52" t="n">
-        <v>112261</v>
+        <v>111996</v>
       </c>
       <c r="R52" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="S52" t="n">
         <v>18</v>
@@ -10065,13 +10061,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.249</v>
+        <v>0.246</v>
       </c>
       <c r="Q53" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="R53" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="S53" t="n">
         <v>16</v>
@@ -10247,13 +10243,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.379</v>
+        <v>0.382</v>
       </c>
       <c r="Q54" t="n">
-        <v>1724</v>
+        <v>1711</v>
       </c>
       <c r="R54" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="S54" t="n">
         <v>39</v>
@@ -10429,13 +10425,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="Q55" t="n">
-        <v>1482</v>
+        <v>1456</v>
       </c>
       <c r="R55" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="S55" t="n">
         <v>13</v>
@@ -10614,10 +10610,10 @@
         <v>0.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="R56" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="S56" t="n">
         <v>9</v>
@@ -12318,70 +12314,70 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>25.59</v>
+        <v>171.54</v>
       </c>
       <c r="D45" t="n">
-        <v>29.77</v>
+        <v>182.69</v>
       </c>
       <c r="E45" t="n">
-        <v>-14</v>
+        <v>-6.1</v>
       </c>
       <c r="F45" t="n">
-        <v>69.03</v>
+        <v>69.05</v>
       </c>
       <c r="G45" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>171.54</v>
+        <v>490.25</v>
       </c>
       <c r="D46" t="n">
-        <v>182.69</v>
+        <v>545.03</v>
       </c>
       <c r="E46" t="n">
-        <v>-6.1</v>
+        <v>-10.1</v>
       </c>
       <c r="F46" t="n">
-        <v>69.05</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
@@ -12423,70 +12419,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>490.25</v>
+        <v>54.05</v>
       </c>
       <c r="D48" t="n">
-        <v>545.03</v>
+        <v>60.15</v>
       </c>
       <c r="E48" t="n">
         <v>-10.1</v>
       </c>
       <c r="F48" t="n">
-        <v>69.90000000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>54.05</v>
+        <v>25.59</v>
       </c>
       <c r="D49" t="n">
-        <v>60.15</v>
+        <v>29.77</v>
       </c>
       <c r="E49" t="n">
-        <v>-10.1</v>
+        <v>-14</v>
       </c>
       <c r="F49" t="n">
-        <v>73.01000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-15/enriched_analysis.xlsx
+++ b/output/2026-09-15/enriched_analysis.xlsx
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.757</v>
+        <v>3.695</v>
       </c>
       <c r="Q2" t="n">
-        <v>2819</v>
+        <v>2866</v>
       </c>
       <c r="R2" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.147</v>
+        <v>0.145</v>
       </c>
       <c r="Q4" t="n">
-        <v>2140</v>
+        <v>2160</v>
       </c>
       <c r="R4" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="S4" t="n">
         <v>-3</v>
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.902</v>
+        <v>0.916</v>
       </c>
       <c r="Q5" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="R5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="S5" t="n">
         <v>17</v>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.058</v>
+        <v>0.061</v>
       </c>
       <c r="Q6" t="n">
-        <v>1420</v>
+        <v>1344</v>
       </c>
       <c r="R6" t="n">
-        <v>19.1</v>
+        <v>18.1</v>
       </c>
       <c r="S6" t="n">
         <v>55</v>
@@ -1908,7 +1908,7 @@
         <v>0.013</v>
       </c>
       <c r="Q8" t="n">
-        <v>16141</v>
+        <v>16188</v>
       </c>
       <c r="R8" t="n">
         <v>20.5</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>2560</v>
+        <v>2574</v>
       </c>
       <c r="R9" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.884</v>
+        <v>2.902</v>
       </c>
       <c r="Q11" t="n">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="R11" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -3178,7 +3178,7 @@
         <v>0.047</v>
       </c>
       <c r="Q15" t="n">
-        <v>15253</v>
+        <v>15239</v>
       </c>
       <c r="R15" t="n">
         <v>38.8</v>
@@ -3485,16 +3485,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3502,91 +3502,87 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
         <v>-1</v>
       </c>
       <c r="I17" t="n">
-        <v>195.52</v>
+        <v>13.79</v>
       </c>
       <c r="J17" t="n">
-        <v>170.45</v>
+        <v>12.79</v>
       </c>
       <c r="K17" t="n">
-        <v>14.7</v>
+        <v>7.8</v>
       </c>
       <c r="L17" t="n">
-        <v>67.54000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="M17" t="n">
-        <v>0.26</v>
+        <v>2.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.1</v>
+        <v>0.538</v>
       </c>
       <c r="Q17" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="R17" t="n">
-        <v>27.9</v>
+        <v>1257</v>
       </c>
       <c r="S17" t="n">
-        <v>24</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.87</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>-31</v>
+        <v>-98</v>
       </c>
       <c r="V17" t="n">
-        <v>3.36</v>
+        <v>0.01</v>
       </c>
       <c r="W17" t="n">
-        <v>4.96</v>
+        <v>2.46</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="Y17" t="b">
         <v>1</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.97</v>
-      </c>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
-        <v>179.59</v>
+        <v>11.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>162.55</v>
+        <v>13.32</v>
       </c>
       <c r="AC17" t="n">
-        <v>37.5</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>170.4518641810919</v>
+        <v>12.74905965615859</v>
       </c>
       <c r="AE17" t="n">
-        <v>14.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -3596,83 +3592,83 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>3293200</v>
       </c>
       <c r="AT17" t="n">
-        <v>5120374</v>
+        <v>6351341</v>
       </c>
       <c r="AU17" t="n">
-        <v>5120374</v>
+        <v>14063235</v>
       </c>
       <c r="AV17" t="n">
-        <v>5120374</v>
+        <v>21553624</v>
       </c>
       <c r="AW17" t="n">
-        <v>5120374</v>
+        <v>21553624</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>3293200</v>
       </c>
       <c r="AY17" t="n">
-        <v>5120374</v>
+        <v>14063235</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA17" t="n">
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>0.2342</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3684,114 +3680,118 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
         <v>-1</v>
       </c>
       <c r="I18" t="n">
-        <v>13.79</v>
+        <v>597.9</v>
       </c>
       <c r="J18" t="n">
-        <v>12.79</v>
+        <v>614.84</v>
       </c>
       <c r="K18" t="n">
-        <v>7.8</v>
+        <v>-2.8</v>
       </c>
       <c r="L18" t="n">
-        <v>69.12</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1</v>
+        <v>4.52</v>
       </c>
       <c r="N18" t="n">
+        <v>34</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1094</v>
+      </c>
+      <c r="R18" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="S18" t="n">
         <v>21</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="T18" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>23</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>576.96</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>513.15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>614.8401686157193</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>11-09-2026</t>
         </is>
       </c>
-      <c r="P18" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>387</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1249</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
-        <v>-98</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Y18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>12.74905965615859</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="AL18" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AM18" t="n">
         <v>4</v>
@@ -3800,61 +3800,61 @@
         <v>3</v>
       </c>
       <c r="AO18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AS18" t="n">
-        <v>3293200</v>
+        <v>2486819</v>
       </c>
       <c r="AT18" t="n">
-        <v>6351341</v>
+        <v>2555826</v>
       </c>
       <c r="AU18" t="n">
-        <v>14063235</v>
+        <v>21426404</v>
       </c>
       <c r="AV18" t="n">
-        <v>21553624</v>
+        <v>21768420</v>
       </c>
       <c r="AW18" t="n">
-        <v>21553624</v>
+        <v>40764834</v>
       </c>
       <c r="AX18" t="n">
-        <v>3293200</v>
+        <v>2486819</v>
       </c>
       <c r="AY18" t="n">
-        <v>14063235</v>
+        <v>21426404</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.2342</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3862,91 +3862,91 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H19" t="n">
         <v>-1</v>
       </c>
       <c r="I19" t="n">
-        <v>597.9</v>
+        <v>195.52</v>
       </c>
       <c r="J19" t="n">
-        <v>614.84</v>
+        <v>170.45</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.8</v>
+        <v>14.7</v>
       </c>
       <c r="L19" t="n">
-        <v>64.68000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>4.52</v>
+        <v>0.26</v>
       </c>
       <c r="N19" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.413</v>
+        <v>0.099</v>
       </c>
       <c r="Q19" t="n">
-        <v>1094</v>
+        <v>263</v>
       </c>
       <c r="R19" t="n">
-        <v>55.7</v>
+        <v>28.1</v>
       </c>
       <c r="S19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.11</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>-31</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>3.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.58</v>
+        <v>4.96</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>-110</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>576.96</v>
+        <v>179.59</v>
       </c>
       <c r="AB19" t="n">
-        <v>513.15</v>
+        <v>162.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>24.9</v>
+        <v>37.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>614.8401686157193</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AE19" t="n">
-        <v>-2.8</v>
+        <v>14.7</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -3956,63 +3956,63 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="AM19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>2486819</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2555826</v>
+        <v>5120374</v>
       </c>
       <c r="AU19" t="n">
-        <v>21426404</v>
+        <v>5120374</v>
       </c>
       <c r="AV19" t="n">
-        <v>21768420</v>
+        <v>5120374</v>
       </c>
       <c r="AW19" t="n">
-        <v>40764834</v>
+        <v>5120374</v>
       </c>
       <c r="AX19" t="n">
-        <v>2486819</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>21426404</v>
+        <v>5120374</v>
       </c>
       <c r="AZ19" t="n">
         <v>2</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.1161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="Q20" t="n">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="R20" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S20" t="n">
         <v>-8</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.098</v>
+        <v>1.093</v>
       </c>
       <c r="Q22" t="n">
-        <v>9357</v>
+        <v>9392</v>
       </c>
       <c r="R22" t="n">
         <v>12.4</v>
@@ -4623,13 +4623,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.199</v>
+        <v>0.202</v>
       </c>
       <c r="Q23" t="n">
-        <v>868</v>
+        <v>857</v>
       </c>
       <c r="R23" t="n">
-        <v>8.529999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="S23" t="n">
         <v>7</v>
@@ -4811,7 +4811,7 @@
         <v>366</v>
       </c>
       <c r="R24" t="n">
-        <v>5.91</v>
+        <v>5.92</v>
       </c>
       <c r="S24" t="n">
         <v>118</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.198</v>
+        <v>0.199</v>
       </c>
       <c r="Q25" t="n">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="R25" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="S25" t="n">
         <v>19</v>
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.599</v>
+        <v>0.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="R30" t="n">
         <v>673</v>
@@ -6442,7 +6442,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>52086</v>
+        <v>52098</v>
       </c>
       <c r="R33" t="n">
         <v>44.1</v>
@@ -6621,13 +6621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.216</v>
+        <v>0.219</v>
       </c>
       <c r="Q34" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R34" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="S34" t="n">
         <v>12</v>
@@ -7168,7 +7168,7 @@
         <v>0.002</v>
       </c>
       <c r="Q37" t="n">
-        <v>340311</v>
+        <v>339959</v>
       </c>
       <c r="R37" t="n">
         <v>18.7</v>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="Q38" t="n">
-        <v>4990</v>
+        <v>5038</v>
       </c>
       <c r="R38" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
       <c r="S38" t="n">
         <v>-25</v>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.291</v>
+        <v>2.288</v>
       </c>
       <c r="Q40" t="n">
-        <v>24327</v>
+        <v>24364</v>
       </c>
       <c r="R40" t="n">
         <v>30.8</v>
@@ -8075,13 +8075,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.399</v>
+        <v>0.406</v>
       </c>
       <c r="Q42" t="n">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="R42" t="n">
-        <v>99.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S42" t="n">
         <v>246</v>
@@ -9347,7 +9347,7 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
-        <v>68.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S49" t="n">
         <v>-1</v>
@@ -9882,7 +9882,7 @@
         <v>0.053</v>
       </c>
       <c r="Q52" t="n">
-        <v>8847</v>
+        <v>8846</v>
       </c>
       <c r="R52" t="n">
         <v>15</v>
@@ -10243,13 +10243,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="Q54" t="n">
-        <v>1714</v>
+        <v>1709</v>
       </c>
       <c r="R54" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="S54" t="n">
         <v>39</v>
@@ -10610,7 +10610,7 @@
         <v>0.008</v>
       </c>
       <c r="Q56" t="n">
-        <v>111981</v>
+        <v>111919</v>
       </c>
       <c r="R56" t="n">
         <v>32.2</v>
@@ -11516,66 +11516,66 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>195.52</v>
+        <v>13.79</v>
       </c>
       <c r="D17" t="n">
-        <v>170.45</v>
+        <v>12.79</v>
       </c>
       <c r="E17" t="n">
-        <v>14.7</v>
+        <v>7.8</v>
       </c>
       <c r="F17" t="n">
-        <v>67.54000000000001</v>
+        <v>69.12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.26</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.79</v>
+        <v>597.9</v>
       </c>
       <c r="D18" t="n">
-        <v>12.79</v>
+        <v>614.84</v>
       </c>
       <c r="E18" t="n">
-        <v>7.8</v>
+        <v>-2.8</v>
       </c>
       <c r="F18" t="n">
-        <v>69.12</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>4.52</v>
       </c>
       <c r="H18" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -11586,35 +11586,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>597.9</v>
+        <v>195.52</v>
       </c>
       <c r="D19" t="n">
-        <v>614.84</v>
+        <v>170.45</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8</v>
+        <v>14.7</v>
       </c>
       <c r="F19" t="n">
-        <v>64.68000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>4.52</v>
+        <v>0.26</v>
       </c>
       <c r="H19" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">

--- a/output/2026-09-15/enriched_analysis.xlsx
+++ b/output/2026-09-15/enriched_analysis.xlsx
@@ -7841,16 +7841,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7858,87 +7858,87 @@
         </is>
       </c>
       <c r="E41" t="n">
+        <v>15</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" t="n">
         <v>9</v>
       </c>
-      <c r="F41" t="n">
-        <v>16</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>410.7</v>
+        <v>411.65</v>
       </c>
       <c r="J41" t="n">
-        <v>417.34</v>
+        <v>454.71</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.6</v>
+        <v>-9.5</v>
       </c>
       <c r="L41" t="n">
-        <v>61.75</v>
+        <v>70.55</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6899999999999999</v>
+        <v>14.28</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.042</v>
+        <v>0.405</v>
       </c>
       <c r="Q41" t="n">
-        <v>1626</v>
+        <v>3530</v>
       </c>
       <c r="R41" t="n">
-        <v>21.2</v>
+        <v>24.7</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="V41" t="n">
-        <v>3.37</v>
+        <v>6.41</v>
       </c>
       <c r="W41" t="n">
-        <v>23.3</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="X41" t="n">
-        <v>0.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="n">
-        <v>441.42</v>
+        <v>440.27</v>
       </c>
       <c r="AB41" t="n">
-        <v>484.24</v>
+        <v>432.25</v>
       </c>
       <c r="AC41" t="n">
-        <v>-21.1</v>
+        <v>5.9</v>
       </c>
       <c r="AD41" t="n">
-        <v>417.3421638870492</v>
+        <v>461.9236485595079</v>
       </c>
       <c r="AE41" t="n">
-        <v>-1.6</v>
+        <v>-10.9</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
@@ -7947,68 +7947,68 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AL41" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="AM41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AR41" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AS41" t="n">
-        <v>13863272</v>
+        <v>40550895</v>
       </c>
       <c r="AT41" t="n">
-        <v>13863272</v>
+        <v>40550895</v>
       </c>
       <c r="AU41" t="n">
-        <v>13863272</v>
+        <v>40550895</v>
       </c>
       <c r="AV41" t="n">
-        <v>13863272</v>
+        <v>224084705</v>
       </c>
       <c r="AW41" t="n">
-        <v>13863272</v>
+        <v>224084705</v>
       </c>
       <c r="AX41" t="n">
-        <v>13863272</v>
+        <v>40550895</v>
       </c>
       <c r="AY41" t="n">
-        <v>13863272</v>
+        <v>40550895</v>
       </c>
       <c r="AZ41" t="n">
         <v>1</v>
@@ -8387,16 +8387,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8404,10 +8404,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -8416,145 +8416,145 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>479.65</v>
+        <v>410.7</v>
       </c>
       <c r="J44" t="n">
-        <v>545.03</v>
+        <v>417.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-12</v>
+        <v>-1.6</v>
       </c>
       <c r="L44" t="n">
-        <v>69.90000000000001</v>
+        <v>61.75</v>
       </c>
       <c r="M44" t="n">
-        <v>1.09</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
       <c r="Q44" t="n">
-        <v>3033</v>
+        <v>1626</v>
       </c>
       <c r="R44" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="S44" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T44" t="n">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="U44" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>3.73</v>
+        <v>3.37</v>
       </c>
       <c r="W44" t="n">
-        <v>19.8</v>
+        <v>23.3</v>
       </c>
       <c r="X44" t="n">
-        <v>0.62</v>
+        <v>0.01</v>
       </c>
       <c r="Y44" t="b">
         <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="AA44" t="n">
-        <v>519.6900000000001</v>
+        <v>441.42</v>
       </c>
       <c r="AB44" t="n">
-        <v>553.04</v>
+        <v>484.24</v>
       </c>
       <c r="AC44" t="n">
-        <v>-1</v>
+        <v>-21.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>545.03455</v>
+        <v>417.3421638870492</v>
       </c>
       <c r="AE44" t="n">
-        <v>-12</v>
+        <v>-1.6</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="AM44" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>13863272</v>
       </c>
       <c r="AZ44" t="n">
         <v>1</v>
@@ -8563,18 +8563,18 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -8598,73 +8598,75 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>710.9</v>
+        <v>479.65</v>
       </c>
       <c r="J45" t="n">
-        <v>815.16</v>
+        <v>545.03</v>
       </c>
       <c r="K45" t="n">
-        <v>-12.8</v>
+        <v>-12</v>
       </c>
       <c r="L45" t="n">
-        <v>73.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.172</v>
+        <v>0.036</v>
       </c>
       <c r="Q45" t="n">
-        <v>720</v>
+        <v>3033</v>
       </c>
       <c r="R45" t="n">
-        <v>13.1</v>
+        <v>20.6</v>
       </c>
       <c r="S45" t="n">
-        <v>185</v>
+        <v>17</v>
       </c>
       <c r="T45" t="n">
-        <v>11.55</v>
+        <v>97</v>
       </c>
       <c r="U45" t="n">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="V45" t="n">
-        <v>6.84</v>
+        <v>3.73</v>
       </c>
       <c r="W45" t="n">
-        <v>50.7</v>
+        <v>19.8</v>
       </c>
       <c r="X45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Y45" t="b">
         <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>16.07</v>
+        <v>40</v>
       </c>
       <c r="AA45" t="n">
-        <v>733.79</v>
-      </c>
-      <c r="AB45" t="inlineStr"/>
+        <v>519.6900000000001</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>553.04</v>
+      </c>
       <c r="AC45" t="n">
-        <v>-21.8</v>
+        <v>-1</v>
       </c>
       <c r="AD45" t="n">
-        <v>815.1570095913809</v>
+        <v>545.03455</v>
       </c>
       <c r="AE45" t="n">
-        <v>-12.8</v>
+        <v>-12</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -8683,22 +8685,22 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AM45" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -8713,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS45" t="n">
         <v>0</v>
@@ -8728,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>12408320</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
@@ -8737,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA45" t="n">
         <v>0</v>
@@ -8931,16 +8933,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8957,112 +8959,110 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>51.61</v>
+        <v>710.9</v>
       </c>
       <c r="J47" t="n">
-        <v>60.15</v>
+        <v>815.16</v>
       </c>
       <c r="K47" t="n">
-        <v>-14.2</v>
+        <v>-12.8</v>
       </c>
       <c r="L47" t="n">
-        <v>73.01000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="M47" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.201</v>
+        <v>0.172</v>
       </c>
       <c r="Q47" t="n">
-        <v>448</v>
+        <v>720</v>
       </c>
       <c r="R47" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
       <c r="S47" t="n">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="T47" t="n">
-        <v>21</v>
+        <v>11.55</v>
       </c>
       <c r="U47" t="n">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="V47" t="n">
-        <v>1.22</v>
+        <v>6.84</v>
       </c>
       <c r="W47" t="n">
-        <v>12</v>
+        <v>50.7</v>
       </c>
       <c r="X47" t="n">
-        <v>0.58</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y47" t="b">
         <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.4</v>
+        <v>16.07</v>
       </c>
       <c r="AA47" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>58.53</v>
-      </c>
+        <v>733.79</v>
+      </c>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>-9.1</v>
+        <v>-21.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>60.1322085106383</v>
+        <v>815.1570095913809</v>
       </c>
       <c r="AE47" t="n">
-        <v>-14.2</v>
+        <v>-12.8</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AK47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AL47" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="AM47" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
         <v>3</v>
@@ -9089,10 +9089,10 @@
         <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>14131069</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>14131069</v>
+        <v>12408320</v>
       </c>
       <c r="AX47" t="n">
         <v>0</v>
@@ -9101,7 +9101,7 @@
         <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA47" t="n">
         <v>0</v>
@@ -9293,12 +9293,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -9310,117 +9310,121 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>-1</v>
       </c>
       <c r="I49" t="n">
-        <v>25.15</v>
+        <v>51.61</v>
       </c>
       <c r="J49" t="n">
-        <v>29.77</v>
+        <v>60.15</v>
       </c>
       <c r="K49" t="n">
-        <v>-15.5</v>
+        <v>-14.2</v>
       </c>
       <c r="L49" t="n">
-        <v>69.03</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="N49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>448</v>
+      </c>
       <c r="R49" t="n">
-        <v>68.40000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="S49" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="T49" t="n">
-        <v>0.4</v>
+        <v>21</v>
       </c>
       <c r="U49" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="V49" t="n">
-        <v>0.59</v>
+        <v>1.22</v>
       </c>
       <c r="W49" t="n">
-        <v>-0.18</v>
+        <v>12</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="Y49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>21.51</v>
+        <v>3.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>27.06</v>
+        <v>57.18</v>
       </c>
       <c r="AB49" t="n">
-        <v>24.71</v>
+        <v>58.53</v>
       </c>
       <c r="AC49" t="n">
-        <v>25.1</v>
+        <v>-9.1</v>
       </c>
       <c r="AD49" t="n">
-        <v>29.69418572675427</v>
+        <v>60.1322085106383</v>
       </c>
       <c r="AE49" t="n">
-        <v>-15.3</v>
+        <v>-14.2</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AK49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AL49" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="AM49" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -9432,10 +9436,10 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AS49" t="n">
         <v>0</v>
@@ -9447,10 +9451,10 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>14131069</v>
       </c>
       <c r="AW49" t="n">
-        <v>2451267</v>
+        <v>14131069</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
@@ -9645,16 +9649,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -9662,137 +9666,133 @@
         </is>
       </c>
       <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>9</v>
+      </c>
+      <c r="G51" t="n">
+        <v>13</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="J51" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N51" t="n">
         <v>7</v>
       </c>
-      <c r="F51" t="n">
-        <v>4</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="S51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>26</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>29.69418572675427</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
         <v>9</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>411.65</v>
-      </c>
-      <c r="J51" t="n">
-        <v>474.82</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-13.3</v>
-      </c>
-      <c r="L51" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="M51" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="N51" t="n">
-        <v>5</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="P51" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3530</v>
-      </c>
-      <c r="R51" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2</v>
-      </c>
-      <c r="T51" t="n">
-        <v>127</v>
-      </c>
-      <c r="U51" t="n">
-        <v>-14</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="W51" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>440.27</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>432.25</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>474.9692297340662</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>-13.3</v>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="AK51" t="n">
+      <c r="AL51" t="n">
+        <v>91</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="n">
         <v>7</v>
       </c>
-      <c r="AL51" t="n">
-        <v>41</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>34</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>8</v>
-      </c>
       <c r="AS51" t="n">
         <v>0</v>
       </c>
@@ -9803,10 +9803,10 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>183533810</v>
+        <v>0</v>
       </c>
       <c r="AW51" t="n">
-        <v>183533810</v>
+        <v>2451267</v>
       </c>
       <c r="AX51" t="n">
         <v>0</v>
@@ -12356,35 +12356,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>410.7</v>
+        <v>411.65</v>
       </c>
       <c r="D41" t="n">
-        <v>417.34</v>
+        <v>454.71</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6</v>
+        <v>-9.5</v>
       </c>
       <c r="F41" t="n">
-        <v>61.75</v>
+        <v>70.55</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6899999999999999</v>
+        <v>14.28</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
     </row>
@@ -12461,70 +12461,70 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>479.65</v>
+        <v>410.7</v>
       </c>
       <c r="D44" t="n">
-        <v>545.03</v>
+        <v>417.34</v>
       </c>
       <c r="E44" t="n">
-        <v>-12</v>
+        <v>-1.6</v>
       </c>
       <c r="F44" t="n">
-        <v>69.90000000000001</v>
+        <v>61.75</v>
       </c>
       <c r="G44" t="n">
-        <v>1.09</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>710.9</v>
+        <v>479.65</v>
       </c>
       <c r="D45" t="n">
-        <v>815.16</v>
+        <v>545.03</v>
       </c>
       <c r="E45" t="n">
-        <v>-12.8</v>
+        <v>-12</v>
       </c>
       <c r="F45" t="n">
-        <v>73.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
@@ -12566,35 +12566,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>51.61</v>
+        <v>710.9</v>
       </c>
       <c r="D47" t="n">
-        <v>60.15</v>
+        <v>815.16</v>
       </c>
       <c r="E47" t="n">
-        <v>-14.2</v>
+        <v>-12.8</v>
       </c>
       <c r="F47" t="n">
-        <v>73.01000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
     </row>
@@ -12636,35 +12636,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25.15</v>
+        <v>51.61</v>
       </c>
       <c r="D49" t="n">
-        <v>29.77</v>
+        <v>60.15</v>
       </c>
       <c r="E49" t="n">
-        <v>-15.5</v>
+        <v>-14.2</v>
       </c>
       <c r="F49" t="n">
-        <v>69.03</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>
@@ -12706,35 +12706,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>THE MOTOR &amp; GENERAL FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>411.65</v>
+        <v>25.15</v>
       </c>
       <c r="D51" t="n">
-        <v>474.82</v>
+        <v>29.77</v>
       </c>
       <c r="E51" t="n">
-        <v>-13.3</v>
+        <v>-15.5</v>
       </c>
       <c r="F51" t="n">
-        <v>70.55</v>
+        <v>69.03</v>
       </c>
       <c r="G51" t="n">
-        <v>10.22</v>
+        <v>0.35</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
